--- a/artfynd/A 11142-2020 artfynd.xlsx
+++ b/artfynd/A 11142-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126490292</v>
+        <v>126490291</v>
       </c>
       <c r="B2" t="n">
         <v>98339</v>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382142</v>
+        <v>382162</v>
       </c>
       <c r="R2" t="n">
-        <v>6593672</v>
+        <v>6593712</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I innerslänt och dikesbotten på östra sidan vägen</t>
+          <t>I innerslänt och dikesbotten på östra sidan vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126490291</v>
+        <v>126490292</v>
       </c>
       <c r="B3" t="n">
         <v>98339</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382162</v>
+        <v>382142</v>
       </c>
       <c r="R3" t="n">
-        <v>6593712</v>
+        <v>6593672</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I innerslänt och dikesbotten på östra sidan vägen.</t>
+          <t>I innerslänt och dikesbotten på östra sidan vägen</t>
         </is>
       </c>
       <c r="AD3" t="b">
